--- a/summary_2026-05-20.xlsx
+++ b/summary_2026-05-20.xlsx
@@ -58571,13 +58571,13 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" s="11" t="n">
         <v>734</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E4" s="11" t="n">
         <v>864</v>
@@ -58596,10 +58596,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D5" t="n">
         <v>74</v>
@@ -58649,10 +58649,10 @@
         <v>59</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>1618</v>
@@ -59482,23 +59482,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Yana Borg Debono Grech</t>
+          <t>Annabelle Cilia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Yana Borg Debono Grech</t>
+          <t>Annabelle Cilia</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1936238287021126</t>
+          <t>993268813185002</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -59517,7 +59517,7 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Olaf McKay</t>
+          <t>Yana Borg Debono Grech</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
@@ -59528,12 +59528,12 @@
       <c r="C26" s="11" t="inlineStr"/>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Olaf McKay</t>
+          <t>Yana Borg Debono Grech</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>1695147474855752</t>
+          <t>1936238287021126</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -59552,7 +59552,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Eric Plumpton</t>
+          <t>Olaf McKay</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -59563,12 +59563,12 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Eric Plumpton</t>
+          <t>Olaf McKay</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>971288432363582</t>
+          <t>1695147474855752</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -60462,23 +60462,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Duncan Borg Myatt</t>
+          <t>Ray Abela</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PN</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Duncan Borg Myatt</t>
+          <t>Ray Abela</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>3276604689166967</t>
+          <t>2115618699296224</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -60497,7 +60497,7 @@
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>Ray Abela</t>
+          <t>Edward Cassar Delia</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
@@ -60508,12 +60508,12 @@
       <c r="C54" s="11" t="inlineStr"/>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Ray Abela</t>
+          <t>Edward Cassar Delia</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>2115618699296224</t>
+          <t>949145677752982</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -60532,7 +60532,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Edward Cassar Delia</t>
+          <t>Lorna Borg Vassallo</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -60543,12 +60543,12 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Edward Cassar Delia</t>
+          <t>Lorna Borġ Vassallo</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>949145677752982</t>
+          <t>982543764707676</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -60567,23 +60567,23 @@
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>Lorna Borg Vassallo</t>
+          <t>John Baptist Camilleri</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PN</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr"/>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Lorna Borġ Vassallo</t>
+          <t>John Baptist Camilleri</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>982543764707676</t>
+          <t>35349534414693500</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -60593,7 +60593,7 @@
       </c>
       <c r="G56" s="11" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr"/>
@@ -60602,23 +60602,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>John Baptist Camilleri</t>
+          <t>Katya De Giovanni</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PN</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>John Baptist Camilleri</t>
+          <t>Katya De Giovanni</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>35349534414693500</t>
+          <t>26625959597085054</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -60628,7 +60628,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -60637,7 +60637,7 @@
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>Katya De Giovanni</t>
+          <t>Edward Cassar Delia</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
@@ -60648,12 +60648,12 @@
       <c r="C58" s="11" t="inlineStr"/>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Katya De Giovanni</t>
+          <t>Edward Cassar Delia</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>26625959597085054</t>
+          <t>2050566099220285</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -60663,7 +60663,7 @@
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr"/>
@@ -60672,7 +60672,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Edward Cassar Delia</t>
+          <t>Nigel Vella</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -60683,12 +60683,12 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Edward Cassar Delia</t>
+          <t>Nigel Vella</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2050566099220285</t>
+          <t>1478044677100859</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -60698,7 +60698,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -60707,7 +60707,7 @@
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>Nigel Vella</t>
+          <t>Lorna Borg Vassallo</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
@@ -60718,12 +60718,12 @@
       <c r="C60" s="11" t="inlineStr"/>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Nigel Vella</t>
+          <t>Lorna Borġ Vassallo</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>1478044677100859</t>
+          <t>942778361908557</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
@@ -60733,7 +60733,7 @@
       </c>
       <c r="G60" s="11" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr"/>
@@ -60758,7 +60758,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>942778361908557</t>
+          <t>984647040762034</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -60768,7 +60768,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -60777,23 +60777,23 @@
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>Lorna Borg Vassallo</t>
+          <t>Annabelle Cilia</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PN</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr"/>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Lorna Borġ Vassallo</t>
+          <t>Annabelle Cilia</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>984647040762034</t>
+          <t>839614662108675</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -60803,7 +60803,7 @@
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr"/>
